--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU_05/HRM/post DFS_HRM-2031-0212/Panel 02/Coupon front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU05_Coupon_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU_05/HRM/post DFS_HRM-2031-0212/Panel 02/Coupon front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU05_Coupon_Front_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.94406</v>
+        <v>16.95008</v>
       </c>
       <c r="D2" t="n">
-        <v>16.96865</v>
+        <v>16.85636</v>
       </c>
       <c r="E2" t="n">
-        <v>16.81299</v>
+        <v>16.8693</v>
       </c>
       <c r="F2" t="n">
-        <v>42.88154</v>
+        <v>43.51184</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05194</v>
+        <v>0.05178</v>
       </c>
       <c r="H2" t="n">
-        <v>1.84875</v>
+        <v>1.86892</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.25361</v>
+        <v>17.08585</v>
       </c>
       <c r="D3" t="n">
-        <v>16.72514</v>
+        <v>16.84961</v>
       </c>
       <c r="E3" t="n">
-        <v>17.39822</v>
+        <v>16.91813</v>
       </c>
       <c r="F3" t="n">
-        <v>43.89988</v>
+        <v>42.7011</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0514</v>
+        <v>0.05234</v>
       </c>
       <c r="H3" t="n">
-        <v>1.85773</v>
+        <v>1.85103</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17.27873</v>
+        <v>17.1763</v>
       </c>
       <c r="D4" t="n">
-        <v>16.78178</v>
+        <v>16.81617</v>
       </c>
       <c r="E4" t="n">
-        <v>16.9255</v>
+        <v>17.01889</v>
       </c>
       <c r="F4" t="n">
-        <v>43.58805</v>
+        <v>43.23793</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0515</v>
+        <v>0.05161</v>
       </c>
       <c r="H4" t="n">
-        <v>1.83672</v>
+        <v>1.89726</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.89183</v>
+        <v>16.83882</v>
       </c>
       <c r="D6" t="n">
-        <v>16.36729</v>
+        <v>15.67204</v>
       </c>
       <c r="E6" t="n">
-        <v>16.40696</v>
+        <v>16.83239</v>
       </c>
       <c r="F6" t="n">
-        <v>22.10815</v>
+        <v>22.11143</v>
       </c>
       <c r="G6" t="n">
-        <v>34.97649</v>
+        <v>34.99197</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.73958</v>
+        <v>16.77201</v>
       </c>
       <c r="D7" t="n">
-        <v>16.35686</v>
+        <v>16.12701</v>
       </c>
       <c r="E7" t="n">
-        <v>16.73089</v>
+        <v>16.57316</v>
       </c>
       <c r="F7" t="n">
-        <v>22.31268</v>
+        <v>22.42384</v>
       </c>
       <c r="G7" t="n">
-        <v>35.10744</v>
+        <v>34.80772</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.99849</v>
+        <v>16.6011</v>
       </c>
       <c r="D8" t="n">
-        <v>16.12916</v>
+        <v>16.40339</v>
       </c>
       <c r="E8" t="n">
-        <v>16.70785</v>
+        <v>16.43587</v>
       </c>
       <c r="F8" t="n">
-        <v>22.34405</v>
+        <v>22.14061</v>
       </c>
       <c r="G8" t="n">
-        <v>34.58669</v>
+        <v>34.26597</v>
       </c>
     </row>
   </sheetData>
